--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8407,0.0198,0.0036,0.1064</t>
-  </si>
-  <si>
-    <t>0.0146,0.0046,0.0016,0.9904</t>
-  </si>
-  <si>
-    <t>0.9836,0.0021,0.0005,0.0077</t>
-  </si>
-  <si>
-    <t>0.1866,0.0021,0.0019,0.9060</t>
-  </si>
-  <si>
-    <t>0.9972,0.0007,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0039,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9931,0.0037,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.8122,0.0109,0.2483,0.0018</t>
-  </si>
-  <si>
-    <t>0.0707,0.0216,0.9380,0.0016</t>
-  </si>
-  <si>
-    <t>0.7100,0.0056,0.4621,0.0004</t>
-  </si>
-  <si>
-    <t>0.0091,0.0011,0.9902,0.0017</t>
-  </si>
-  <si>
-    <t>0.9020,0.0014,0.1741,0.0013</t>
-  </si>
-  <si>
-    <t>0.0009,0.9973,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0065,0.0006</t>
-  </si>
-  <si>
-    <t>0.0768,0.9320,0.0043,0.0021</t>
-  </si>
-  <si>
-    <t>0.0015,0.9936,0.0029,0.0026</t>
-  </si>
-  <si>
-    <t>0.0033,0.9921,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.9577,0.0025,0.0244,0.0050</t>
-  </si>
-  <si>
-    <t>0.8507,0.0029,0.1108,0.0088</t>
-  </si>
-  <si>
-    <t>0.0071,0.0040,0.9937,0.0004</t>
-  </si>
-  <si>
-    <t>0.0151,0.0167,0.9625,0.0210</t>
-  </si>
-  <si>
-    <t>0.0243,0.0035,0.9778,0.0016</t>
-  </si>
-  <si>
-    <t>0.0111,0.0013,0.9805,0.0071</t>
-  </si>
-  <si>
-    <t>0.0145,0.0014,0.9835,0.0041</t>
-  </si>
-  <si>
-    <t>0.4935,0.6672,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.4946,0.1301,0.5080,0.0049</t>
-  </si>
-  <si>
-    <t>0.0056,0.0243,0.9836,0.0046</t>
-  </si>
-  <si>
-    <t>0.0013,0.9910,0.0361,0.0002</t>
-  </si>
-  <si>
-    <t>0.8624,0.0518,0.0926,0.0079</t>
-  </si>
-  <si>
-    <t>0.9914,0.0039,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.8890,0.0983,0.0132,0.0071</t>
-  </si>
-  <si>
-    <t>0.0035,0.9857,0.0297,0.0073</t>
-  </si>
-  <si>
-    <t>0.2160,0.2836,0.3365,0.0337</t>
-  </si>
-  <si>
-    <t>0.0270,0.0168,0.9651,0.0071</t>
-  </si>
-  <si>
-    <t>0.0058,0.0133,0.9813,0.0089</t>
-  </si>
-  <si>
-    <t>0.0140,0.0015,0.9851,0.0036</t>
-  </si>
-  <si>
-    <t>0.0187,0.1293,0.9744,0.0013</t>
-  </si>
-  <si>
-    <t>0.0024,0.9863,0.0098,0.0004</t>
-  </si>
-  <si>
-    <t>0.0037,0.0013,0.9939,0.0017</t>
-  </si>
-  <si>
-    <t>0.0019,0.5973,0.0029,0.9744</t>
-  </si>
-  <si>
-    <t>0.0023,0.9907,0.0039,0.0034</t>
-  </si>
-  <si>
-    <t>0.0012,0.9918,0.0348,0.0016</t>
-  </si>
-  <si>
-    <t>0.0002,0.9976,0.0122,0.0018</t>
-  </si>
-  <si>
-    <t>0.0022,0.0613,0.9748,0.0035</t>
-  </si>
-  <si>
-    <t>0.0147,0.0838,0.9760,0.0029</t>
-  </si>
-  <si>
-    <t>0.0034,0.0023,0.9909,0.0044</t>
-  </si>
-  <si>
-    <t>0.0224,0.0035,0.9704,0.0061</t>
-  </si>
-  <si>
-    <t>0.0072,0.0213,0.9821,0.0045</t>
-  </si>
-  <si>
-    <t>0.0073,0.0905,0.9776,0.0049</t>
-  </si>
-  <si>
-    <t>0.9894,0.0086,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9937,0.0023,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9883,0.0041,0.0035,0.0013</t>
-  </si>
-  <si>
-    <t>0.0013,0.0170,0.9944,0.0093</t>
-  </si>
-  <si>
-    <t>0.9905,0.0039,0.0037,0.0008</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0006,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.9456,0.9100,0.0008</t>
-  </si>
-  <si>
-    <t>0.0111,0.0094,0.9893,0.0013</t>
-  </si>
-  <si>
-    <t>0.0089,0.0375,0.9747,0.0050</t>
-  </si>
-  <si>
-    <t>0.0006,0.9380,0.9727,0.0010</t>
-  </si>
-  <si>
-    <t>0.0016,0.0040,0.9951,0.0014</t>
-  </si>
-  <si>
-    <t>0.1068,0.9132,0.0060,0.0006</t>
-  </si>
-  <si>
-    <t>0.0137,0.9854,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.4563,0.0238,0.7183,0.0038</t>
-  </si>
-  <si>
-    <t>0.8564,0.0672,0.1050,0.0034</t>
-  </si>
-  <si>
-    <t>0.0008,0.0025,0.9969,0.0025</t>
-  </si>
-  <si>
-    <t>0.0025,0.8641,0.9482,0.0008</t>
-  </si>
-  <si>
-    <t>0.0029,0.9537,0.7297,0.0010</t>
-  </si>
-  <si>
-    <t>0.0040,0.9772,0.0917,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9786,0.9576,0.0004</t>
-  </si>
-  <si>
-    <t>0.0792,0.0016,0.0049,0.9505</t>
-  </si>
-  <si>
-    <t>0.0008,0.0013,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0023,0.0008,0.0006,0.9981</t>
-  </si>
-  <si>
-    <t>0.0073,0.0020,0.0003,0.9966</t>
-  </si>
-  <si>
-    <t>0.0035,0.0001,0.0004,0.9984</t>
-  </si>
-  <si>
-    <t>0.0073,0.0019,0.0011,0.9953</t>
-  </si>
-  <si>
-    <t>0.0036,0.9513,0.8247,0.0024</t>
-  </si>
-  <si>
-    <t>0.0002,0.9260,0.9938,0.0002</t>
-  </si>
-  <si>
-    <t>0.0099,0.8528,0.4116,0.0096</t>
-  </si>
-  <si>
-    <t>0.0018,0.9397,0.9000,0.0011</t>
-  </si>
-  <si>
-    <t>0.0006,0.9760,0.8365,0.0001</t>
-  </si>
-  <si>
-    <t>0.0069,0.9408,0.2567,0.0064</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9906,0.0083,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9940,0.0063,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9943,0.0049,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9953,0.0023,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9975,0.0014,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9910,0.0151,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9822,0.0272,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0013,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9977,0.0010,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9966,0.0024,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0000,0.0019</t>
-  </si>
-  <si>
-    <t>0.0110,0.0010,0.9884,0.0012</t>
-  </si>
-  <si>
-    <t>0.0434,0.0532,0.9299,0.0218</t>
-  </si>
-  <si>
-    <t>0.9538,0.0010,0.0320,0.0025</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9957,0.0026</t>
-  </si>
-  <si>
-    <t>0.0021,0.9944,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.0028,0.9944,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0048,0.9832,0.0072,0.0183</t>
-  </si>
-  <si>
-    <t>0.0116,0.9766,0.0149,0.0028</t>
-  </si>
-  <si>
-    <t>0.0073,0.9846,0.0068,0.0031</t>
-  </si>
-  <si>
-    <t>0.0014,0.9952,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.6253,0.4963,0.0151,0.0027</t>
-  </si>
-  <si>
-    <t>0.9297,0.0290,0.0455,0.0022</t>
-  </si>
-  <si>
-    <t>0.2132,0.0066,0.8321,0.0070</t>
-  </si>
-  <si>
-    <t>0.2438,0.0481,0.6750,0.0391</t>
-  </si>
-  <si>
-    <t>0.6758,0.0235,0.4139,0.0097</t>
-  </si>
-  <si>
-    <t>0.0818,0.0242,0.0463,0.9075</t>
-  </si>
-  <si>
-    <t>0.0098,0.9797,0.0055,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.9947,0.0040,0.0015</t>
-  </si>
-  <si>
-    <t>0.0006,0.9921,0.0061,0.0450</t>
-  </si>
-  <si>
-    <t>0.0004,0.9900,0.8359,0.0002</t>
-  </si>
-  <si>
-    <t>0.0030,0.9941,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.8244,0.2560,0.0080,0.0006</t>
-  </si>
-  <si>
-    <t>0.8853,0.1379,0.0069,0.0029</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0007,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9958,0.0013,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9783,0.0052,0.0121,0.0014</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0024,0.0008,0.0032</t>
-  </si>
-  <si>
-    <t>0.9955,0.0014,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9628,0.0089,0.0208,0.0039</t>
-  </si>
-  <si>
-    <t>0.0055,0.8772,0.8929,0.0040</t>
-  </si>
-  <si>
-    <t>0.0021,0.2562,0.9810,0.0002</t>
-  </si>
-  <si>
-    <t>0.0055,0.0207,0.9835,0.0016</t>
-  </si>
-  <si>
-    <t>0.0218,0.1132,0.9577,0.0029</t>
-  </si>
-  <si>
-    <t>0.9945,0.0010,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.8519,0.0030,0.2396,0.0025</t>
-  </si>
-  <si>
-    <t>0.0489,0.0010,0.9571,0.0071</t>
-  </si>
-  <si>
-    <t>0.9531,0.0057,0.0448,0.0010</t>
-  </si>
-  <si>
-    <t>0.4220,0.0004,0.0001,0.8613</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.0006,0.9992</t>
-  </si>
-  <si>
-    <t>0.0036,0.0007,0.0005,0.9977</t>
-  </si>
-  <si>
-    <t>0.0361,0.0005,0.0018,0.9864</t>
-  </si>
-  <si>
-    <t>0.0007,0.9611,0.7484,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0011,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.0571,0.9356,0.0053,0.0066</t>
-  </si>
-  <si>
-    <t>0.9930,0.0021,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.5064,0.5529,0.0292,0.0038</t>
-  </si>
-  <si>
-    <t>0.9962,0.0005,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.0565,0.0068,0.2322,0.8044</t>
-  </si>
-  <si>
-    <t>0.9920,0.0014,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.0165,0.0142,0.8673,0.2457</t>
-  </si>
-  <si>
-    <t>0.3319,0.0007,0.0040,0.7627</t>
-  </si>
-  <si>
-    <t>0.9756,0.0036,0.0033,0.0071</t>
-  </si>
-  <si>
-    <t>0.3872,0.5911,0.0713,0.0223</t>
-  </si>
-  <si>
-    <t>0.9808,0.0074,0.0049,0.0007</t>
-  </si>
-  <si>
-    <t>0.9721,0.0252,0.0040,0.0012</t>
-  </si>
-  <si>
-    <t>0.2769,0.6828,0.0662,0.0040</t>
-  </si>
-  <si>
-    <t>0.9712,0.0100,0.0152,0.0013</t>
-  </si>
-  <si>
-    <t>0.9825,0.0095,0.0049,0.0008</t>
-  </si>
-  <si>
-    <t>0.9953,0.0028,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0010,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9807,0.0130,0.0029,0.0033</t>
-  </si>
-  <si>
-    <t>0.9963,0.0003,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9920,0.0017,0.0012,0.0017</t>
-  </si>
-  <si>
-    <t>0.9940,0.0024,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9936,0.0008,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.5776,0.4452,0.0019,0.0057</t>
-  </si>
-  <si>
-    <t>0.3028,0.7719,0.0015,0.0021</t>
-  </si>
-  <si>
-    <t>0.3641,0.7839,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.7016,0.3304,0.0908,0.0126</t>
-  </si>
-  <si>
-    <t>0.9803,0.0256,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9561,0.0193,0.0232,0.0027</t>
-  </si>
-  <si>
-    <t>0.9928,0.0021,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9843,0.0092,0.0011,0.0026</t>
-  </si>
-  <si>
-    <t>0.0005,0.0116,0.9981,0.0013</t>
-  </si>
-  <si>
-    <t>0.9300,0.0652,0.0216,0.0025</t>
-  </si>
-  <si>
-    <t>0.0034,0.0159,0.9939,0.0003</t>
-  </si>
-  <si>
-    <t>0.0074,0.0072,0.9887,0.0009</t>
-  </si>
-  <si>
-    <t>0.0054,0.0025,0.9911,0.0047</t>
-  </si>
-  <si>
-    <t>0.0138,0.0324,0.9762,0.0012</t>
-  </si>
-  <si>
-    <t>0.0054,0.0024,0.9939,0.0011</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9980,0.0009</t>
-  </si>
-  <si>
-    <t>0.0065,0.0026,0.9861,0.0057</t>
-  </si>
-  <si>
-    <t>0.0919,0.0451,0.8729,0.0099</t>
-  </si>
-  <si>
-    <t>0.0677,0.0036,0.9523,0.0028</t>
-  </si>
-  <si>
-    <t>0.3581,0.0633,0.7080,0.0144</t>
-  </si>
-  <si>
-    <t>0.5840,0.1042,0.3937,0.0131</t>
-  </si>
-  <si>
-    <t>0.1510,0.2478,0.6960,0.0286</t>
-  </si>
-  <si>
-    <t>0.6563,0.0677,0.3631,0.0034</t>
-  </si>
-  <si>
-    <t>0.4575,0.0040,0.6990,0.0036</t>
-  </si>
-  <si>
-    <t>0.2066,0.0835,0.7030,0.0597</t>
-  </si>
-  <si>
-    <t>0.0778,0.9482,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.7809,0.3982,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.8507,0.2421,0.0034,0.0025</t>
-  </si>
-  <si>
-    <t>0.9860,0.0176,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.5887,0.5885,0.0019,0.0011</t>
-  </si>
-  <si>
-    <t>0.8932,0.0418,0.0447,0.0048</t>
-  </si>
-  <si>
-    <t>0.7426,0.0027,0.1845,0.0213</t>
-  </si>
-  <si>
-    <t>0.8800,0.0065,0.0398,0.0381</t>
-  </si>
-  <si>
-    <t>0.8580,0.0164,0.1291,0.0220</t>
-  </si>
-  <si>
-    <t>0.7585,0.0043,0.3083,0.0057</t>
-  </si>
-  <si>
-    <t>0.0138,0.0087,0.9606,0.0329</t>
-  </si>
-  <si>
-    <t>0.0450,0.0385,0.9006,0.0257</t>
-  </si>
-  <si>
-    <t>0.0137,0.0523,0.9699,0.0110</t>
-  </si>
-  <si>
-    <t>0.0928,0.0017,0.9269,0.0018</t>
-  </si>
-  <si>
-    <t>0.0059,0.0659,0.9747,0.0016</t>
-  </si>
-  <si>
-    <t>0.9962,0.0010,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9968,0.0017,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9835,0.0038,0.0003,0.0073</t>
-  </si>
-  <si>
-    <t>0.9925,0.0067,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9781,0.0198,0.0042,0.0021</t>
-  </si>
-  <si>
-    <t>0.9877,0.0053,0.0023,0.0015</t>
-  </si>
-  <si>
-    <t>0.9899,0.0030,0.0008,0.0032</t>
-  </si>
-  <si>
-    <t>0.9958,0.0015,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.0065,0.0098,0.9905,0.0019</t>
-  </si>
-  <si>
-    <t>0.0752,0.4727,0.8118,0.0318</t>
-  </si>
-  <si>
-    <t>0.9389,0.0023,0.0398,0.0034</t>
-  </si>
-  <si>
-    <t>0.0262,0.0027,0.9817,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0067,0.9928,0.0059</t>
-  </si>
-  <si>
-    <t>0.1144,0.0303,0.8934,0.0067</t>
-  </si>
-  <si>
-    <t>0.0023,0.0034,0.9944,0.0030</t>
-  </si>
-  <si>
-    <t>0.0623,0.0079,0.9292,0.0171</t>
-  </si>
-  <si>
-    <t>0.0007,0.0165,0.9969,0.0007</t>
-  </si>
-  <si>
-    <t>0.0058,0.0341,0.8385,0.1690</t>
-  </si>
-  <si>
-    <t>0.1592,0.0953,0.7737,0.0046</t>
-  </si>
-  <si>
-    <t>0.4142,0.0015,0.5857,0.0079</t>
-  </si>
-  <si>
-    <t>0.8464,0.0007,0.2050,0.0024</t>
-  </si>
-  <si>
-    <t>0.9547,0.0029,0.0420,0.0010</t>
-  </si>
-  <si>
-    <t>0.9881,0.0061,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.9946,0.0055,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0014,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9694,0.0461,0.0026,0.0012</t>
-  </si>
-  <si>
-    <t>0.9967,0.0007,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9878,0.0174,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0076,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0053,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.0128,0.0059,0.9770,0.0023</t>
-  </si>
-  <si>
-    <t>0.0079,0.1039,0.9838,0.0012</t>
-  </si>
-  <si>
-    <t>0.0194,0.0453,0.9151,0.0130</t>
-  </si>
-  <si>
-    <t>0.0912,0.0082,0.9235,0.0012</t>
-  </si>
-  <si>
-    <t>0.0059,0.0010,0.9906,0.0011</t>
-  </si>
-  <si>
-    <t>0.0326,0.0066,0.9554,0.0149</t>
-  </si>
-  <si>
-    <t>0.0134,0.0104,0.9643,0.0271</t>
-  </si>
-  <si>
-    <t>0.0147,0.0040,0.9257,0.0484</t>
-  </si>
-  <si>
-    <t>0.4476,0.0129,0.0102,0.5888</t>
-  </si>
-  <si>
-    <t>0.0279,0.0071,0.0010,0.9874</t>
-  </si>
-  <si>
-    <t>0.0729,0.0009,0.0018,0.9695</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0011,0.9988</t>
-  </si>
-  <si>
-    <t>0.0034,0.0005,0.0007,0.9976</t>
-  </si>
-  <si>
-    <t>0.8409,0.0150,0.0035,0.1227</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9233,0.0289,0.0251,0.0182</t>
+  </si>
+  <si>
+    <t>0.0050,0.0005,0.0002,0.9976</t>
+  </si>
+  <si>
+    <t>0.9661,0.0014,0.0004,0.0351</t>
+  </si>
+  <si>
+    <t>0.5037,0.0136,0.0009,0.5780</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0011,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0016,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0034,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.7092,0.0452,0.2772,0.0223</t>
+  </si>
+  <si>
+    <t>0.0957,0.0078,0.9152,0.0071</t>
+  </si>
+  <si>
+    <t>0.2508,0.0010,0.9081,0.0002</t>
+  </si>
+  <si>
+    <t>0.0920,0.0179,0.8978,0.0046</t>
+  </si>
+  <si>
+    <t>0.8014,0.0033,0.2930,0.0020</t>
+  </si>
+  <si>
+    <t>0.0009,0.9967,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.9914,0.0071,0.0024</t>
+  </si>
+  <si>
+    <t>0.0190,0.9753,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.0054,0.9882,0.0117,0.0019</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.2553,0.0160,0.7512,0.0303</t>
+  </si>
+  <si>
+    <t>0.2626,0.0343,0.7133,0.0387</t>
+  </si>
+  <si>
+    <t>0.0037,0.0034,0.9937,0.0006</t>
+  </si>
+  <si>
+    <t>0.1267,0.0136,0.8976,0.0068</t>
+  </si>
+  <si>
+    <t>0.0350,0.0011,0.9733,0.0030</t>
+  </si>
+  <si>
+    <t>0.0124,0.0026,0.9789,0.0048</t>
+  </si>
+  <si>
+    <t>0.0151,0.0004,0.9836,0.0017</t>
+  </si>
+  <si>
+    <t>0.5253,0.6389,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.7471,0.0352,0.2990,0.0027</t>
+  </si>
+  <si>
+    <t>0.0033,0.0076,0.9872,0.0062</t>
+  </si>
+  <si>
+    <t>0.0203,0.8528,0.0940,0.0003</t>
+  </si>
+  <si>
+    <t>0.9665,0.0046,0.0200,0.0015</t>
+  </si>
+  <si>
+    <t>0.9899,0.0042,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.3106,0.7318,0.0051,0.0022</t>
+  </si>
+  <si>
+    <t>0.0050,0.9843,0.0255,0.0033</t>
+  </si>
+  <si>
+    <t>0.0772,0.6823,0.1525,0.0081</t>
+  </si>
+  <si>
+    <t>0.3016,0.0055,0.7223,0.0054</t>
+  </si>
+  <si>
+    <t>0.0175,0.0200,0.9728,0.0049</t>
+  </si>
+  <si>
+    <t>0.0149,0.0029,0.9826,0.0035</t>
+  </si>
+  <si>
+    <t>0.0181,0.3133,0.9499,0.0028</t>
+  </si>
+  <si>
+    <t>0.0018,0.9926,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0057,0.9914,0.0018</t>
+  </si>
+  <si>
+    <t>0.0150,0.7708,0.0146,0.7955</t>
+  </si>
+  <si>
+    <t>0.0038,0.9829,0.0023,0.0241</t>
+  </si>
+  <si>
+    <t>0.0001,0.9986,0.0085,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.9889,0.0226,0.0034</t>
+  </si>
+  <si>
+    <t>0.0058,0.0202,0.9775,0.0076</t>
+  </si>
+  <si>
+    <t>0.0019,0.0209,0.9933,0.0014</t>
+  </si>
+  <si>
+    <t>0.0354,0.0064,0.9598,0.0074</t>
+  </si>
+  <si>
+    <t>0.0119,0.0004,0.9883,0.0026</t>
+  </si>
+  <si>
+    <t>0.0167,0.0302,0.9752,0.0023</t>
+  </si>
+  <si>
+    <t>0.0113,0.0430,0.9755,0.0020</t>
+  </si>
+  <si>
+    <t>0.9831,0.0213,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9511,0.0232,0.0319,0.0028</t>
+  </si>
+  <si>
+    <t>0.9791,0.0153,0.0040,0.0031</t>
+  </si>
+  <si>
+    <t>0.0009,0.0087,0.9962,0.0050</t>
+  </si>
+  <si>
+    <t>0.9918,0.0062,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9915,0.0066,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9927,0.0044,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0018,0.8929,0.9619,0.0010</t>
+  </si>
+  <si>
+    <t>0.0337,0.0595,0.9620,0.0036</t>
+  </si>
+  <si>
+    <t>0.0054,0.0296,0.9778,0.0108</t>
+  </si>
+  <si>
+    <t>0.0004,0.9285,0.9900,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.0128,0.9943,0.0019</t>
+  </si>
+  <si>
+    <t>0.0287,0.9749,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0184,0.9871,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7717,0.0054,0.4303,0.0024</t>
+  </si>
+  <si>
+    <t>0.8800,0.0343,0.1281,0.0023</t>
+  </si>
+  <si>
+    <t>0.0016,0.0082,0.9955,0.0010</t>
+  </si>
+  <si>
+    <t>0.0139,0.8134,0.6509,0.0015</t>
+  </si>
+  <si>
+    <t>0.0064,0.9398,0.6347,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.9950,0.0165,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9838,0.4570,0.0021</t>
+  </si>
+  <si>
+    <t>0.0287,0.0002,0.0003,0.9922</t>
+  </si>
+  <si>
+    <t>0.0056,0.0004,0.0001,0.9976</t>
+  </si>
+  <si>
+    <t>0.0035,0.0012,0.0000,0.9983</t>
+  </si>
+  <si>
+    <t>0.0154,0.0031,0.0025,0.9895</t>
+  </si>
+  <si>
+    <t>0.0034,0.0006,0.0007,0.9977</t>
+  </si>
+  <si>
+    <t>0.0029,0.0013,0.0009,0.9973</t>
+  </si>
+  <si>
+    <t>0.0011,0.9879,0.6093,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.5851,0.9919,0.0010</t>
+  </si>
+  <si>
+    <t>0.0055,0.9540,0.0514,0.0063</t>
+  </si>
+  <si>
+    <t>0.0194,0.0848,0.9598,0.0103</t>
+  </si>
+  <si>
+    <t>0.0024,0.9458,0.6695,0.0004</t>
+  </si>
+  <si>
+    <t>0.0043,0.8977,0.4692,0.0131</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9916,0.0135,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9797,0.0322,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9912,0.0073,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9950,0.0046,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0036,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9896,0.0080,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.9895,0.0117,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0026,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.0096,0.0013,0.9875,0.0022</t>
+  </si>
+  <si>
+    <t>0.1580,0.0105,0.8454,0.0131</t>
+  </si>
+  <si>
+    <t>0.9456,0.0103,0.0128,0.0110</t>
+  </si>
+  <si>
+    <t>0.0136,0.0012,0.9832,0.0050</t>
+  </si>
+  <si>
+    <t>0.0029,0.9914,0.0063,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.9950,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.0082,0.9834,0.0039,0.0044</t>
+  </si>
+  <si>
+    <t>0.0090,0.9785,0.0199,0.0033</t>
+  </si>
+  <si>
+    <t>0.0047,0.9899,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.9966,0.0056,0.0007</t>
+  </si>
+  <si>
+    <t>0.6215,0.4270,0.0492,0.0034</t>
+  </si>
+  <si>
+    <t>0.6008,0.0376,0.4975,0.0084</t>
+  </si>
+  <si>
+    <t>0.0671,0.0017,0.9609,0.0007</t>
+  </si>
+  <si>
+    <t>0.3246,0.1761,0.4529,0.0714</t>
+  </si>
+  <si>
+    <t>0.9182,0.0022,0.1421,0.0010</t>
+  </si>
+  <si>
+    <t>0.0581,0.0665,0.2216,0.7750</t>
+  </si>
+  <si>
+    <t>0.0014,0.9945,0.0109,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.9984,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9953,0.0052,0.0126</t>
+  </si>
+  <si>
+    <t>0.0004,0.9898,0.8388,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.9946,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.8626,0.2361,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9182,0.1127,0.0028,0.0026</t>
+  </si>
+  <si>
+    <t>0.9974,0.0011,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0029,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9862,0.0035,0.0032,0.0028</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9899,0.0019,0.0011,0.0030</t>
+  </si>
+  <si>
+    <t>0.9931,0.0022,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.9887,0.0034,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.0026,0.7647,0.9576,0.0044</t>
+  </si>
+  <si>
+    <t>0.0305,0.2870,0.7348,0.0007</t>
+  </si>
+  <si>
+    <t>0.0155,0.0318,0.9777,0.0017</t>
+  </si>
+  <si>
+    <t>0.0468,0.0459,0.9435,0.0022</t>
+  </si>
+  <si>
+    <t>0.9931,0.0002,0.0065,0.0001</t>
+  </si>
+  <si>
+    <t>0.8805,0.0019,0.2124,0.0014</t>
+  </si>
+  <si>
+    <t>0.2468,0.0018,0.8641,0.0032</t>
+  </si>
+  <si>
+    <t>0.7939,0.0723,0.1376,0.0114</t>
+  </si>
+  <si>
+    <t>0.5182,0.0034,0.0008,0.7117</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0034,0.0047,0.0011,0.9965</t>
+  </si>
+  <si>
+    <t>0.2556,0.0003,0.0001,0.9375</t>
+  </si>
+  <si>
+    <t>0.0019,0.9257,0.5671,0.0009</t>
+  </si>
+  <si>
+    <t>0.9945,0.0010,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.0369,0.9621,0.0010,0.0031</t>
+  </si>
+  <si>
+    <t>0.9748,0.0084,0.0054,0.0058</t>
+  </si>
+  <si>
+    <t>0.0501,0.9445,0.0082,0.0031</t>
+  </si>
+  <si>
+    <t>0.9920,0.0010,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.3345,0.0444,0.0351,0.6350</t>
+  </si>
+  <si>
+    <t>0.9947,0.0016,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0033,0.0085,0.8699,0.4028</t>
+  </si>
+  <si>
+    <t>0.8628,0.0005,0.0072,0.0670</t>
+  </si>
+  <si>
+    <t>0.9249,0.0007,0.0006,0.1077</t>
+  </si>
+  <si>
+    <t>0.0195,0.9434,0.0246,0.0660</t>
+  </si>
+  <si>
+    <t>0.9955,0.0020,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9736,0.0172,0.0080,0.0010</t>
+  </si>
+  <si>
+    <t>0.5214,0.4378,0.0590,0.0030</t>
+  </si>
+  <si>
+    <t>0.9692,0.0083,0.0249,0.0006</t>
+  </si>
+  <si>
+    <t>0.9759,0.0087,0.0063,0.0021</t>
+  </si>
+  <si>
+    <t>0.9914,0.0045,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9892,0.0063,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.9818,0.0005,0.0008,0.0140</t>
+  </si>
+  <si>
+    <t>0.9826,0.0096,0.0014,0.0038</t>
+  </si>
+  <si>
+    <t>0.9966,0.0009,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0009,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9950,0.0013,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.5855,0.5087,0.0019,0.0031</t>
+  </si>
+  <si>
+    <t>0.4894,0.6628,0.0059,0.0012</t>
+  </si>
+  <si>
+    <t>0.9291,0.0873,0.0060,0.0009</t>
+  </si>
+  <si>
+    <t>0.4338,0.3173,0.4594,0.0105</t>
+  </si>
+  <si>
+    <t>0.9713,0.0167,0.0034,0.0070</t>
+  </si>
+  <si>
+    <t>0.9818,0.0088,0.0031,0.0028</t>
+  </si>
+  <si>
+    <t>0.9887,0.0052,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.8911,0.1432,0.0121,0.0047</t>
+  </si>
+  <si>
+    <t>0.0015,0.0067,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.9798,0.0087,0.0067,0.0014</t>
+  </si>
+  <si>
+    <t>0.0016,0.0042,0.9964,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.0493,0.9871,0.0054</t>
+  </si>
+  <si>
+    <t>0.0112,0.0027,0.9754,0.0158</t>
+  </si>
+  <si>
+    <t>0.0249,0.0235,0.9636,0.0005</t>
+  </si>
+  <si>
+    <t>0.0030,0.0025,0.9960,0.0006</t>
+  </si>
+  <si>
+    <t>0.0014,0.0007,0.9971,0.0013</t>
+  </si>
+  <si>
+    <t>0.0017,0.0055,0.9964,0.0009</t>
+  </si>
+  <si>
+    <t>0.0211,0.0074,0.9528,0.0177</t>
+  </si>
+  <si>
+    <t>0.1446,0.0237,0.8672,0.0084</t>
+  </si>
+  <si>
+    <t>0.2911,0.0167,0.7921,0.0104</t>
+  </si>
+  <si>
+    <t>0.1332,0.0845,0.8772,0.0031</t>
+  </si>
+  <si>
+    <t>0.2965,0.1222,0.5748,0.0034</t>
+  </si>
+  <si>
+    <t>0.5209,0.0981,0.4416,0.0079</t>
+  </si>
+  <si>
+    <t>0.4643,0.0707,0.4663,0.0964</t>
+  </si>
+  <si>
+    <t>0.5168,0.0391,0.5274,0.0073</t>
+  </si>
+  <si>
+    <t>0.6839,0.5292,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.3242,0.8061,0.0043,0.0010</t>
+  </si>
+  <si>
+    <t>0.9087,0.1452,0.0049,0.0022</t>
+  </si>
+  <si>
+    <t>0.9834,0.0203,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.9730,0.0276,0.0043,0.0010</t>
+  </si>
+  <si>
+    <t>0.4649,0.4620,0.1299,0.0171</t>
+  </si>
+  <si>
+    <t>0.9854,0.0011,0.0077,0.0005</t>
+  </si>
+  <si>
+    <t>0.9765,0.0042,0.0071,0.0016</t>
+  </si>
+  <si>
+    <t>0.9377,0.0061,0.0953,0.0010</t>
+  </si>
+  <si>
+    <t>0.8768,0.0132,0.1230,0.0043</t>
+  </si>
+  <si>
+    <t>0.0184,0.0068,0.9713,0.0105</t>
+  </si>
+  <si>
+    <t>0.0091,0.0066,0.9763,0.0054</t>
+  </si>
+  <si>
+    <t>0.0072,0.0543,0.9803,0.0083</t>
+  </si>
+  <si>
+    <t>0.1044,0.0009,0.9362,0.0007</t>
+  </si>
+  <si>
+    <t>0.0144,0.0224,0.9658,0.0016</t>
+  </si>
+  <si>
+    <t>0.9850,0.0088,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9876,0.0123,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9770,0.0124,0.0001,0.0023</t>
+  </si>
+  <si>
+    <t>0.9758,0.0187,0.0043,0.0016</t>
+  </si>
+  <si>
+    <t>0.9965,0.0012,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9936,0.0015,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.9963,0.0011,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.0033,0.0212,0.9877,0.0070</t>
+  </si>
+  <si>
+    <t>0.3859,0.0987,0.6522,0.0107</t>
+  </si>
+  <si>
+    <t>0.9395,0.0074,0.0340,0.0051</t>
+  </si>
+  <si>
+    <t>0.0117,0.0011,0.9832,0.0019</t>
+  </si>
+  <si>
+    <t>0.0009,0.0398,0.9945,0.0020</t>
+  </si>
+  <si>
+    <t>0.0397,0.0246,0.9433,0.0054</t>
+  </si>
+  <si>
+    <t>0.0008,0.0054,0.9959,0.0051</t>
+  </si>
+  <si>
+    <t>0.0052,0.0210,0.9646,0.0181</t>
+  </si>
+  <si>
+    <t>0.0012,0.0090,0.9947,0.0016</t>
+  </si>
+  <si>
+    <t>0.0489,0.0080,0.9287,0.0276</t>
+  </si>
+  <si>
+    <t>0.0716,0.0809,0.8664,0.0075</t>
+  </si>
+  <si>
+    <t>0.9026,0.0008,0.1052,0.0028</t>
+  </si>
+  <si>
+    <t>0.9362,0.0002,0.0601,0.0014</t>
+  </si>
+  <si>
+    <t>0.9522,0.0032,0.0432,0.0023</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9917,0.0085,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9773,0.0166,0.0068,0.0027</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0042,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9808,0.0205,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.0195,0.0145,0.9566,0.0030</t>
+  </si>
+  <si>
+    <t>0.0168,0.0429,0.9651,0.0018</t>
+  </si>
+  <si>
+    <t>0.0078,0.0469,0.9504,0.0028</t>
+  </si>
+  <si>
+    <t>0.0230,0.0111,0.9753,0.0009</t>
+  </si>
+  <si>
+    <t>0.0155,0.0034,0.9792,0.0027</t>
+  </si>
+  <si>
+    <t>0.0961,0.0005,0.6467,0.0775</t>
+  </si>
+  <si>
+    <t>0.0209,0.0165,0.9637,0.0129</t>
+  </si>
+  <si>
+    <t>0.0312,0.0004,0.8080,0.0521</t>
+  </si>
+  <si>
+    <t>0.8302,0.0018,0.0020,0.1868</t>
+  </si>
+  <si>
+    <t>0.0082,0.0091,0.0061,0.9910</t>
+  </si>
+  <si>
+    <t>0.0542,0.0014,0.0018,0.9756</t>
+  </si>
+  <si>
+    <t>0.0030,0.0001,0.0004,0.9983</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0007,0.9988</t>
+  </si>
+  <si>
+    <t>0.6081,0.0159,0.0089,0.4147</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +2010,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2164,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2920,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2937,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +3004,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3133,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3175,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3553,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3956,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4071,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4099,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4138,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4169,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4379,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4631,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4642,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4659,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4684,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4768,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4782,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5188,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5454,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
